--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
@@ -1418,11 +1418,6 @@
           <t>173</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1430,11 +1425,6 @@
           <t>174</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1442,11 +1432,6 @@
           <t>175</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1454,11 +1439,6 @@
           <t>176</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1466,11 +1446,6 @@
           <t>177</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1478,11 +1453,6 @@
           <t>178</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1490,11 +1460,6 @@
           <t>179</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1502,11 +1467,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>1, 2A1, 2A2, 2B, 2C, 2D, 3</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1514,11 +1474,6 @@
           <t>180</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3, 4A, 4B, 5</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1526,11 +1481,6 @@
           <t>181</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1538,11 +1488,6 @@
           <t>182</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1550,11 +1495,6 @@
           <t>183</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1562,11 +1502,6 @@
           <t>184</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5A, 5B, 6</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1574,11 +1509,6 @@
           <t>185</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1586,11 +1516,6 @@
           <t>186</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1598,11 +1523,6 @@
           <t>187</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1610,11 +1530,6 @@
           <t>188</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5A, 5B, 5C, 5D, 5E</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1622,11 +1537,6 @@
           <t>189</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>1, 2A1, 2A2, 2A3, 2B, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1634,11 +1544,6 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3, 4A, 4B, 5</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1646,11 +1551,6 @@
           <t>190</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1658,11 +1558,6 @@
           <t>191</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1670,11 +1565,6 @@
           <t>192</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 2A1, 2A2, 2B, 3A, 3B, 3C1, 3C2, 4</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1682,11 +1572,6 @@
           <t>193</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 1A, 1B, 2A, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1694,11 +1579,6 @@
           <t>194</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1706,11 +1586,6 @@
           <t>195</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 3</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1718,11 +1593,6 @@
           <t>196</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1730,11 +1600,6 @@
           <t>197</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1742,11 +1607,6 @@
           <t>198</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1754,11 +1614,6 @@
           <t>199</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1766,11 +1621,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A1, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 35, 36, 37, 38, 39, 4, 40, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1778,11 +1628,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1790,11 +1635,6 @@
           <t>200</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4A, 4B</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1802,11 +1642,6 @@
           <t>201</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 3C, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1814,11 +1649,6 @@
           <t>202</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1826,11 +1656,6 @@
           <t>203</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1838,11 +1663,6 @@
           <t>204</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 3A, 3C, 4, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1850,11 +1670,6 @@
           <t>205</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1862,11 +1677,6 @@
           <t>206</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1874,11 +1684,6 @@
           <t>207</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1886,11 +1691,6 @@
           <t>208</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1898,11 +1698,6 @@
           <t>209</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1910,11 +1705,6 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1922,11 +1712,6 @@
           <t>210</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1934,11 +1719,6 @@
           <t>211</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1946,11 +1726,6 @@
           <t>212</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1958,11 +1733,6 @@
           <t>213</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1970,11 +1740,6 @@
           <t>214</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4A, 4B, 4C, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1982,11 +1747,6 @@
           <t>215</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1994,11 +1754,6 @@
           <t>216</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2006,11 +1761,6 @@
           <t>217</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3A1, 3A2, 3A3, 3B, 3C1, 3C2, 3D, 3E, 4</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2018,11 +1768,6 @@
           <t>218</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>1A1A, 1A1B, 1A1C, 1A1D, 1A2, 1A3, 1A4, 1B, 2, 3, 4, 5A, 5B, 6</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2030,11 +1775,6 @@
           <t>219</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2042,11 +1782,6 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2054,11 +1789,6 @@
           <t>220</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2066,11 +1796,6 @@
           <t>221</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2078,11 +1803,6 @@
           <t>222</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2090,11 +1810,6 @@
           <t>223</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2102,11 +1817,6 @@
           <t>224</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2114,11 +1824,6 @@
           <t>225</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2126,11 +1831,6 @@
           <t>226</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2138,11 +1838,6 @@
           <t>227</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2150,11 +1845,6 @@
           <t>228</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2162,11 +1852,6 @@
           <t>229</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>1, 10, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2174,11 +1859,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 3A, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2186,11 +1866,6 @@
           <t>230</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2A, 2B, 3, 4A, 4B, 4C</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2198,11 +1873,6 @@
           <t>231</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7A, 7B</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2210,11 +1880,6 @@
           <t>232</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2222,11 +1887,6 @@
           <t>233</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3A, 3B, 4A, 4B, 4C</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2234,11 +1894,6 @@
           <t>234</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>1, 10, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2246,11 +1901,6 @@
           <t>235</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2258,11 +1908,6 @@
           <t>236</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 3C, 4, 5A, 5B, 6A, 6B, 6C, 6D, 6E, 6F</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2270,11 +1915,6 @@
           <t>237</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2282,11 +1922,6 @@
           <t>238</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2294,11 +1929,6 @@
           <t>239</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2306,11 +1936,6 @@
           <t>24</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2318,11 +1943,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3, 4A, 4B</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2330,11 +1950,6 @@
           <t>241</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2342,11 +1957,6 @@
           <t>242</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>1, 10, 2A, 2B, 2C, 2D, 2E, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2354,11 +1964,6 @@
           <t>243</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 2C, 3, 4A, 4B, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2366,11 +1971,6 @@
           <t>244</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 3A, 3B, 3C, 3D, 3E, 4, 5, 6A, 6B, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2378,11 +1978,6 @@
           <t>245</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2390,11 +1985,6 @@
           <t>246</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 2C, 3A, 3B, 3C</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2402,11 +1992,6 @@
           <t>247</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2A, 2B, 3A, 3B, 4A, 4B, 4C, 4D, 4E, 4F, 4G</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2414,11 +1999,6 @@
           <t>248</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 2D, 2E, 2F</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2426,11 +2006,6 @@
           <t>249</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4A, 4B, 5A, 5B, 6</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2438,11 +2013,6 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2450,11 +2020,6 @@
           <t>250</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 1K, 1L, 2, 3A, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2462,11 +2027,6 @@
           <t>251</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4A, 4B</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2474,11 +2034,6 @@
           <t>252</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2486,11 +2041,6 @@
           <t>253</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2498,11 +2048,6 @@
           <t>254</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2510,11 +2055,6 @@
           <t>255</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2522,11 +2062,6 @@
           <t>256</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2534,11 +2069,6 @@
           <t>257</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2546,11 +2076,6 @@
           <t>258</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>1, 10, 2, 3, 4, 5, 6A, 6B, 6C, 7, 8, 9A, 9B, 9C</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2558,11 +2083,6 @@
           <t>259</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2570,11 +2090,6 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3A, 3B, 4, 5, 6, 7, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2582,11 +2097,6 @@
           <t>260</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4, 5, 6, 7A, 7B, 7C</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2594,11 +2104,6 @@
           <t>261</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 3C</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2606,11 +2111,6 @@
           <t>262</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2618,11 +2118,6 @@
           <t>263</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2630,11 +2125,6 @@
           <t>264</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2642,11 +2132,6 @@
           <t>265</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2654,11 +2139,6 @@
           <t>266</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2666,11 +2146,6 @@
           <t>267</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2678,11 +2153,6 @@
           <t>268</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2690,11 +2160,6 @@
           <t>269</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>1A, 1B1, 1B2, 1C, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2702,11 +2167,6 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>10, 1A, 1B, 2, 3A, 3B, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2714,11 +2174,6 @@
           <t>270</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 2C, 2D</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2726,11 +2181,6 @@
           <t>271</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2738,11 +2188,6 @@
           <t>272</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2750,11 +2195,6 @@
           <t>273</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2762,11 +2202,6 @@
           <t>274</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>10, 11, 1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2774,11 +2209,6 @@
           <t>275</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2786,11 +2216,6 @@
           <t>276</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2A, 2B, 2C, 2D, 2E</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2798,11 +2223,6 @@
           <t>277</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2810,11 +2230,6 @@
           <t>278</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2822,11 +2237,6 @@
           <t>279</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2834,11 +2244,6 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2846,11 +2251,6 @@
           <t>280</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2858,11 +2258,6 @@
           <t>281</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2870,11 +2265,6 @@
           <t>282</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2882,11 +2272,6 @@
           <t>283</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2894,11 +2279,6 @@
           <t>284</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 3</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2906,11 +2286,6 @@
           <t>285</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2918,11 +2293,6 @@
           <t>286</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2930,11 +2300,6 @@
           <t>287</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2942,11 +2307,6 @@
           <t>288</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 2</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2954,11 +2314,6 @@
           <t>289</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2966,11 +2321,6 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 2D, 3, 4A1, 4A10, 4A2, 4A3, 4A4, 4A5A, 4A5B, 4A5C, 4A6, 4A7, 4A8, 4A9, 4B</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2978,11 +2328,6 @@
           <t>290</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2990,11 +2335,6 @@
           <t>291</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 3A, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -3002,11 +2342,6 @@
           <t>292</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 2</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -3014,11 +2349,6 @@
           <t>293</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -3026,11 +2356,6 @@
           <t>294</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -3038,11 +2363,6 @@
           <t>295</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -3050,11 +2370,6 @@
           <t>296</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -3062,11 +2377,6 @@
           <t>297</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -3074,11 +2384,6 @@
           <t>298</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -3086,11 +2391,6 @@
           <t>299</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -3098,11 +2398,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 2C, 3A, 3B, 4, 5A, 5B, 5C, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -3110,11 +2405,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -3122,11 +2412,6 @@
           <t>300</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -3134,11 +2419,6 @@
           <t>301</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -3146,11 +2426,6 @@
           <t>302</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -3158,11 +2433,6 @@
           <t>303</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -3170,11 +2440,6 @@
           <t>304</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -3182,11 +2447,6 @@
           <t>305</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -3194,11 +2454,6 @@
           <t>306</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -3206,11 +2461,6 @@
           <t>307</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -3218,11 +2468,6 @@
           <t>308</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -3230,11 +2475,6 @@
           <t>309</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -3242,11 +2482,6 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 3, 4, 5A, 5B, 5C, 6A, 6B</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -3254,11 +2489,6 @@
           <t>310</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 5</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -3266,11 +2496,6 @@
           <t>311</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -3278,11 +2503,6 @@
           <t>312</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -3290,11 +2510,6 @@
           <t>313</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -3302,11 +2517,6 @@
           <t>314</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -3314,11 +2524,6 @@
           <t>315</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>1A, 1B1, 1B2, 1C, 1D, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -3326,11 +2531,6 @@
           <t>316</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>1, 1B, 2A, 2B, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -3338,11 +2538,6 @@
           <t>317</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -3350,11 +2545,6 @@
           <t>318</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -3362,11 +2552,6 @@
           <t>319</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -3374,11 +2559,6 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -3386,11 +2566,6 @@
           <t>320</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -3398,11 +2573,6 @@
           <t>321</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -3410,11 +2580,6 @@
           <t>322</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -3422,11 +2587,6 @@
           <t>323</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -3434,11 +2594,6 @@
           <t>324</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4A, 4B, 5</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -3446,11 +2601,6 @@
           <t>325</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -3458,11 +2608,6 @@
           <t>326</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2, 3, 4, 5, 6, 7</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -3470,11 +2615,6 @@
           <t>327</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3482,11 +2622,6 @@
           <t>328</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3494,11 +2629,6 @@
           <t>329</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3506,11 +2636,6 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 7C</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3518,11 +2643,6 @@
           <t>330</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 2, 3, 5</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3530,11 +2650,6 @@
           <t>331</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 2D, 2E1, 2E2, 3A, 3B, 4A, 4B, 5, 6A, 6B, 6C1, 6C2, 7A, 7B</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3542,11 +2657,6 @@
           <t>332</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3554,11 +2664,6 @@
           <t>333</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3566,11 +2671,6 @@
           <t>334</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3578,11 +2678,6 @@
           <t>335</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3590,11 +2685,6 @@
           <t>336</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>1A1A1, 1A1A2, 1A1B, 1A2, 1A3, 1A4, 1B1A, 1B1B, 1B1C, 1B2, 2A1A, 2A1B, 2A1C, 2A1D, 2A2, 2A3, 2B1, 2B2, 2C1, 2C2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3602,11 +2692,6 @@
           <t>337</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3614,11 +2699,6 @@
           <t>338</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3626,11 +2706,6 @@
           <t>339</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3638,11 +2713,6 @@
           <t>34</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3650,11 +2720,6 @@
           <t>340</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3662,11 +2727,6 @@
           <t>341</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3674,11 +2734,6 @@
           <t>342</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 3</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3686,11 +2741,6 @@
           <t>343</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3698,11 +2748,6 @@
           <t>344</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -3710,11 +2755,6 @@
           <t>345</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3722,11 +2762,6 @@
           <t>346</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3734,11 +2769,6 @@
           <t>347</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3746,11 +2776,6 @@
           <t>348</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3758,11 +2783,6 @@
           <t>349</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3770,11 +2790,6 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -3782,11 +2797,6 @@
           <t>350</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3A, 3B, 3C, 3D, 3E</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -3794,11 +2804,6 @@
           <t>351</t>
         </is>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -3806,11 +2811,6 @@
           <t>352</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -3818,11 +2818,6 @@
           <t>353</t>
         </is>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>1, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 1K, 1L, 1M, 1N, 2A, 2B, 3A, 3B1A, 3B1B, 3B2A, 3B2B, 3B3A, 3B3B, 3C1, 3C10A1, 3C10A2, 3C10B, 3C2, 3C3A1, 3C3A2, 3C3B, 3C4A1, 3C4A2, 3C4B, 3C5A, 3C5B, 3C6A, 3C6B, 3C7A, 3C7B, 3C8A, 3C8B, 3C9A, 3C9B, 3D</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -3830,11 +2825,6 @@
           <t>354</t>
         </is>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 19, 2, 20A, 20B, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 6, 60, 61, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -3842,11 +2832,6 @@
           <t>355A</t>
         </is>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>2A, 2B1, 2B2, 2C, 2D, 2E, 2F</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -3854,11 +2839,6 @@
           <t>355B</t>
         </is>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>2A1, 2A2, 2A3, 2A4A, 2A4B, 2B10, 2B11, 2B12, 2B13, 2B14, 2B15A, 2B15B, 2B16A1, 2B16A2, 2B16B, 2B17, 2B18, 2B19, 2B1A, 2B1B, 2B2, 2B20, 2B21, 2B22, 2B23, 2B24, 2B25, 2B26, 2B27, 2B28, 2B29, 2B3, 2B30, 2B31, 2B32, 2B33, 2B34, 2B35, 2B36A1, 2B36A2, 2B36B, 2B37A, 2B38, 2B39, 2B4, 2B40, 2B41, 2B42, 2B43A1, 2B43B, 2B44, 2B45, 2B46, 2B47A, 2B47B1, 2B47B2, 2B5, 2B61A, 2B61B1, 2B61B2, 2B6A1, 2B6A2A, 2B6A2B, 2B7A1, 2B7A2, 2B7B, 2B7C, 2B8, 2B9, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -3866,11 +2846,6 @@
           <t>356</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A2, 1A3, 1B1, 1B2, 1C1, 1C2A, 1C2B, 1D1, 1D1A1A, 1D2, 1D3A1A, 1D3B, 1D3C, 1E, 1F, 1G1, 1G2, 1H, 1I1, 1I2, 1J1, 1J2, 1K1A, 1K1B, 1K1C, 1K2, 1L, 1M, 1N1, 1N2, 2, 3, 4, 6A, 6B, 7, 8A, 8B, 8C, 9</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -3878,11 +2853,6 @@
           <t>357</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -3890,11 +2860,6 @@
           <t>358</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -3902,11 +2867,6 @@
           <t>359</t>
         </is>
       </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -3914,11 +2874,6 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -3926,11 +2881,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -3938,11 +2888,6 @@
           <t>361</t>
         </is>
       </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -3950,11 +2895,6 @@
           <t>362</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4, 5, 6</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -3962,11 +2902,6 @@
           <t>363</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -3974,11 +2909,6 @@
           <t>364</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -3986,11 +2916,6 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3A, 3B, 4, 5A, 5B</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -3998,11 +2923,6 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -4010,11 +2930,6 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -4022,11 +2937,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -4034,11 +2944,6 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -4046,11 +2951,6 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -4058,11 +2958,6 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -4070,11 +2965,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -4082,11 +2972,6 @@
           <t>44</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -4094,11 +2979,6 @@
           <t>45</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -4106,11 +2986,6 @@
           <t>46</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3A1, 3A2, 3B, 4A, 4B, 4C</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -4118,11 +2993,6 @@
           <t>47</t>
         </is>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -4130,11 +3000,6 @@
           <t>48</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2, 3, 4, 5A, 5B, 6A, 6B, 7A, 7B, 8, 9A, 9B</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -4142,11 +3007,6 @@
           <t>49</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -4154,11 +3014,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 18C, 19, 2, 20, 21, 22, 23, 24A, 24B, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 5A1A1, 6, 7A1A1, 7B, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -4166,11 +3021,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -4178,11 +3028,6 @@
           <t>51</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -4190,11 +3035,6 @@
           <t>52</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -4202,11 +3042,6 @@
           <t>53</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -4214,11 +3049,6 @@
           <t>54</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>1, 10, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -4226,11 +3056,6 @@
           <t>55</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 4, 5, 6A, 6B, 6C, 7, 8A, 8B</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -4238,11 +3063,6 @@
           <t>56</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -4250,11 +3070,6 @@
           <t>57</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 1D, 1E, 2</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -4262,11 +3077,6 @@
           <t>58</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -4274,11 +3084,6 @@
           <t>59</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2A, 2B, 2C, 3</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -4286,11 +3091,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B, 3C, 3D</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -4298,11 +3098,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -4310,11 +3105,6 @@
           <t>61</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 8</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -4322,11 +3112,6 @@
           <t>62</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -4334,11 +3119,6 @@
           <t>63</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -4346,11 +3126,6 @@
           <t>64</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -4358,11 +3133,6 @@
           <t>65</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -4370,11 +3140,6 @@
           <t>66</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -4382,11 +3147,6 @@
           <t>67</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -4394,11 +3154,6 @@
           <t>68</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -4406,11 +3161,6 @@
           <t>69</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -4418,11 +3168,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2, 3A1, 3A2, 3A3, 3B, 4A1, 4A2, 4B</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -4430,11 +3175,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -4442,11 +3182,6 @@
           <t>71</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -4454,11 +3189,6 @@
           <t>72</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -4466,11 +3196,6 @@
           <t>73</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -4478,11 +3203,6 @@
           <t>74</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -4490,11 +3210,6 @@
           <t>75</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -4502,11 +3217,6 @@
           <t>76</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 3A, 3B, 3C</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -4514,11 +3224,6 @@
           <t>77</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>1A1, 1A2, 1B, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -4526,11 +3231,6 @@
           <t>78</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -4538,11 +3238,6 @@
           <t>79</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -4550,11 +3245,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>1, 10, 11, 12, 13A, 13B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -4562,11 +3252,6 @@
           <t>80</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -4574,11 +3259,6 @@
           <t>81</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4, 5</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -4586,11 +3266,6 @@
           <t>82</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2A, 2B, 2C</t>
-        </is>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -4598,11 +3273,6 @@
           <t>83</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 2I, 2J, 3A, 3B, 3C, 3D1, 3D2, 3E, 3F1, 3F2, 3G, 3H1, 3H2, 3I1, 3I2, 3J1, 3J2, 3K, 3L, 3M, 3N, 3O, 3P1, 3P2, 4A1, 4A2, 4B, 4C</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -4610,11 +3280,6 @@
           <t>84</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -4622,11 +3287,6 @@
           <t>85</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -4634,11 +3294,6 @@
           <t>86</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -4646,11 +3301,6 @@
           <t>87</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -4658,11 +3308,6 @@
           <t>88</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -4670,11 +3315,6 @@
           <t>89</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>1, 2, 3A, 3B</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -4682,11 +3322,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>1, 2A1, 2A2, 2B, 2C</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -4694,11 +3329,6 @@
           <t>90</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>1A, 1B, 1C, 2A, 2B</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -4706,11 +3336,6 @@
           <t>91</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -4718,11 +3343,6 @@
           <t>92</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -4730,11 +3350,6 @@
           <t>93</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>1A, 1B, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -4742,11 +3357,6 @@
           <t>94</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 1A, 1B, 2, 3A, 3B, 4, 5, 6, 7A, 7B, 8A1, 8A2, 8B, 9</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -4754,11 +3364,6 @@
           <t>95</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -4766,11 +3371,6 @@
           <t>96</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>1, 10A, 10B, 2, 3, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -4778,11 +3378,6 @@
           <t>97</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>1, 2, 3</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -4790,21 +3385,11 @@
           <t>98</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>10, 11, 12, 13, 14, 15, 16, 1A, 1B, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
-        </is>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
           <t>99</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>1, 2</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
@@ -1418,6 +1418,11 @@
           <t>173</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1425,6 +1430,11 @@
           <t>174</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1432,6 +1442,11 @@
           <t>175</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1439,6 +1454,11 @@
           <t>176</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1446,6 +1466,11 @@
           <t>177</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1453,6 +1478,11 @@
           <t>178</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1460,6 +1490,11 @@
           <t>179</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1467,6 +1502,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 2C, 2D, 3</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1474,6 +1514,11 @@
           <t>180</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1481,6 +1526,11 @@
           <t>181</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1488,6 +1538,11 @@
           <t>182</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1495,6 +1550,11 @@
           <t>183</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1502,6 +1562,11 @@
           <t>184</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1509,6 +1574,11 @@
           <t>185</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1516,6 +1586,11 @@
           <t>186</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1523,6 +1598,11 @@
           <t>187</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1530,6 +1610,11 @@
           <t>188</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 5C, 5D, 5E</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1537,6 +1622,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3, 2B, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1544,6 +1634,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1551,6 +1646,11 @@
           <t>190</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1558,6 +1658,11 @@
           <t>191</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1565,6 +1670,11 @@
           <t>192</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A1, 2A2, 2B, 3A, 3B, 3C1, 3C2, 4</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1572,6 +1682,11 @@
           <t>193</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 2A, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1579,6 +1694,11 @@
           <t>194</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1586,6 +1706,11 @@
           <t>195</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1593,6 +1718,11 @@
           <t>196</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1600,6 +1730,11 @@
           <t>197</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1607,6 +1742,11 @@
           <t>198</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1614,6 +1754,11 @@
           <t>199</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1621,6 +1766,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A1, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 35, 36, 37, 38, 39, 4, 40, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1628,6 +1778,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1635,6 +1790,11 @@
           <t>200</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1642,6 +1802,11 @@
           <t>201</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1649,6 +1814,11 @@
           <t>202</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1656,6 +1826,11 @@
           <t>203</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1663,6 +1838,11 @@
           <t>204</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 3A, 3C, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1670,6 +1850,11 @@
           <t>205</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1677,6 +1862,11 @@
           <t>206</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1684,6 +1874,11 @@
           <t>207</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1691,6 +1886,11 @@
           <t>208</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1698,6 +1898,11 @@
           <t>209</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1705,6 +1910,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1712,6 +1922,11 @@
           <t>210</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1719,6 +1934,11 @@
           <t>211</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1726,6 +1946,11 @@
           <t>212</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1733,6 +1958,11 @@
           <t>213</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1740,6 +1970,11 @@
           <t>214</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 4C, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1747,6 +1982,11 @@
           <t>215</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1754,6 +1994,11 @@
           <t>216</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1761,6 +2006,11 @@
           <t>217</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A1, 3A2, 3A3, 3B, 3C1, 3C2, 3D, 3E, 4</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1768,6 +2018,11 @@
           <t>218</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A1C, 1A1D, 1A2, 1A3, 1A4, 1B, 2, 3, 4, 5A, 5B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1775,6 +2030,11 @@
           <t>219</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1782,6 +2042,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1789,6 +2054,11 @@
           <t>220</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1796,6 +2066,11 @@
           <t>221</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1803,6 +2078,11 @@
           <t>222</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1810,6 +2090,11 @@
           <t>223</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1817,6 +2102,11 @@
           <t>224</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1824,6 +2114,11 @@
           <t>225</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1831,6 +2126,11 @@
           <t>226</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1838,6 +2138,11 @@
           <t>227</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1845,6 +2150,11 @@
           <t>228</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -1852,6 +2162,11 @@
           <t>229</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1, 10, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -1859,6 +2174,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -1866,6 +2186,11 @@
           <t>230</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 3, 4A, 4B, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -1873,6 +2198,11 @@
           <t>231</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -1880,6 +2210,11 @@
           <t>232</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -1887,6 +2222,11 @@
           <t>233</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B, 4A, 4B, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -1894,6 +2234,11 @@
           <t>234</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -1901,6 +2246,11 @@
           <t>235</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -1908,6 +2258,11 @@
           <t>236</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 4, 5A, 5B, 6A, 6B, 6C, 6D, 6E, 6F</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -1915,6 +2270,11 @@
           <t>237</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -1922,6 +2282,11 @@
           <t>238</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -1929,6 +2294,11 @@
           <t>239</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -1936,6 +2306,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -1943,6 +2318,11 @@
           <t>240</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -1950,6 +2330,11 @@
           <t>241</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -1957,6 +2342,11 @@
           <t>242</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1, 10, 2A, 2B, 2C, 2D, 2E, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -1964,6 +2354,11 @@
           <t>243</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3, 4A, 4B, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -1971,6 +2366,11 @@
           <t>244</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3A, 3B, 3C, 3D, 3E, 4, 5, 6A, 6B, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -1978,6 +2378,11 @@
           <t>245</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -1985,6 +2390,11 @@
           <t>246</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -1992,6 +2402,11 @@
           <t>247</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 3A, 3B, 4A, 4B, 4C, 4D, 4E, 4F, 4G</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -1999,6 +2414,11 @@
           <t>248</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 2F</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2006,6 +2426,11 @@
           <t>249</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 5A, 5B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2013,6 +2438,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2020,6 +2450,11 @@
           <t>250</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 1K, 1L, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2027,6 +2462,11 @@
           <t>251</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2034,6 +2474,11 @@
           <t>252</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2041,6 +2486,11 @@
           <t>253</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2048,6 +2498,11 @@
           <t>254</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2055,6 +2510,11 @@
           <t>255</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2062,11 +2522,21 @@
           <t>256</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
           <t>257</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
@@ -2546,6 +2546,11 @@
           <t>258</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6A, 6B, 6C, 7, 8, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2553,6 +2558,11 @@
           <t>259</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2560,6 +2570,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3A, 3B, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2567,6 +2582,11 @@
           <t>260</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6, 7A, 7B, 7C</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2574,6 +2594,11 @@
           <t>261</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2581,6 +2606,11 @@
           <t>262</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2588,6 +2618,11 @@
           <t>263</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2595,6 +2630,11 @@
           <t>264</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2602,6 +2642,11 @@
           <t>265</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2609,6 +2654,11 @@
           <t>266</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2616,6 +2666,11 @@
           <t>267</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2623,6 +2678,11 @@
           <t>268</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2630,6 +2690,11 @@
           <t>269</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2637,6 +2702,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 2, 3A, 3B, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2644,6 +2714,11 @@
           <t>270</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 2D</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2651,6 +2726,11 @@
           <t>271</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2658,6 +2738,11 @@
           <t>272</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2665,6 +2750,11 @@
           <t>273</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2672,6 +2762,11 @@
           <t>274</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>10, 11, 1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2679,6 +2774,11 @@
           <t>275</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2686,6 +2786,11 @@
           <t>276</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 2C, 2D, 2E</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2693,6 +2798,11 @@
           <t>277</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2700,6 +2810,11 @@
           <t>278</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2707,6 +2822,11 @@
           <t>279</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2714,6 +2834,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2721,6 +2846,11 @@
           <t>280</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2728,6 +2858,11 @@
           <t>281</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2735,6 +2870,11 @@
           <t>282</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2742,6 +2882,11 @@
           <t>283</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2749,6 +2894,11 @@
           <t>284</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2756,6 +2906,11 @@
           <t>285</t>
         </is>
       </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2763,6 +2918,11 @@
           <t>286</t>
         </is>
       </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2770,6 +2930,11 @@
           <t>287</t>
         </is>
       </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2777,6 +2942,11 @@
           <t>288</t>
         </is>
       </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2784,6 +2954,11 @@
           <t>289</t>
         </is>
       </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2791,6 +2966,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 2D, 3, 4A1, 4A10, 4A2, 4A3, 4A4, 4A5A, 4A5B, 4A5C, 4A6, 4A7, 4A8, 4A9, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2798,6 +2978,11 @@
           <t>290</t>
         </is>
       </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2805,6 +2990,11 @@
           <t>291</t>
         </is>
       </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2812,6 +3002,11 @@
           <t>292</t>
         </is>
       </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 2</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2819,6 +3014,11 @@
           <t>293</t>
         </is>
       </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2826,6 +3026,11 @@
           <t>294</t>
         </is>
       </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2833,6 +3038,11 @@
           <t>295</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -2840,6 +3050,11 @@
           <t>296</t>
         </is>
       </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -2847,6 +3062,11 @@
           <t>297</t>
         </is>
       </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -2854,6 +3074,11 @@
           <t>298</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -2861,6 +3086,11 @@
           <t>299</t>
         </is>
       </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -2868,6 +3098,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3A, 3B, 4, 5A, 5B, 5C, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -2875,6 +3110,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -2882,6 +3122,11 @@
           <t>300</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -2889,6 +3134,11 @@
           <t>301</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -2896,6 +3146,11 @@
           <t>302</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -2903,6 +3158,11 @@
           <t>303</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -2910,6 +3170,11 @@
           <t>304</t>
         </is>
       </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -2917,6 +3182,11 @@
           <t>305</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -2924,6 +3194,11 @@
           <t>306</t>
         </is>
       </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -2931,6 +3206,11 @@
           <t>307</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -2938,6 +3218,11 @@
           <t>308</t>
         </is>
       </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -2945,6 +3230,11 @@
           <t>309</t>
         </is>
       </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -2952,6 +3242,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3, 4, 5A, 5B, 5C, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -2959,6 +3254,11 @@
           <t>310</t>
         </is>
       </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -2966,6 +3266,11 @@
           <t>311</t>
         </is>
       </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -2973,6 +3278,11 @@
           <t>312</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -2980,6 +3290,11 @@
           <t>313</t>
         </is>
       </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -2987,6 +3302,11 @@
           <t>314</t>
         </is>
       </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -2994,6 +3314,11 @@
           <t>315</t>
         </is>
       </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 1D, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -3001,6 +3326,11 @@
           <t>316</t>
         </is>
       </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1, 1B, 2A, 2B, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -3008,6 +3338,11 @@
           <t>317</t>
         </is>
       </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -3015,6 +3350,11 @@
           <t>318</t>
         </is>
       </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -3022,6 +3362,11 @@
           <t>319</t>
         </is>
       </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -3029,6 +3374,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -3036,6 +3386,11 @@
           <t>320</t>
         </is>
       </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -3043,6 +3398,11 @@
           <t>321</t>
         </is>
       </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -3050,6 +3410,11 @@
           <t>322</t>
         </is>
       </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -3057,6 +3422,11 @@
           <t>323</t>
         </is>
       </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -3064,6 +3434,11 @@
           <t>324</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -3071,6 +3446,11 @@
           <t>325</t>
         </is>
       </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -3078,6 +3458,11 @@
           <t>326</t>
         </is>
       </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -3085,6 +3470,11 @@
           <t>327</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3092,6 +3482,11 @@
           <t>328</t>
         </is>
       </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3099,6 +3494,11 @@
           <t>329</t>
         </is>
       </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3106,6 +3506,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 7C</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3113,6 +3518,11 @@
           <t>330</t>
         </is>
       </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2, 3, 5</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3120,6 +3530,11 @@
           <t>331</t>
         </is>
       </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E1, 2E2, 3A, 3B, 4A, 4B, 5, 6A, 6B, 6C1, 6C2, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3127,6 +3542,11 @@
           <t>332</t>
         </is>
       </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3134,6 +3554,11 @@
           <t>333</t>
         </is>
       </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3141,6 +3566,11 @@
           <t>334</t>
         </is>
       </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3148,6 +3578,11 @@
           <t>335</t>
         </is>
       </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3155,6 +3590,11 @@
           <t>336</t>
         </is>
       </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>1A1A1, 1A1A2, 1A1B, 1A2, 1A3, 1A4, 1B1A, 1B1B, 1B1C, 1B2, 2A1A, 2A1B, 2A1C, 2A1D, 2A2, 2A3, 2B1, 2B2, 2C1, 2C2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3162,11 +3602,21 @@
           <t>337</t>
         </is>
       </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
           <t>338</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
@@ -3626,6 +3626,11 @@
           <t>339</t>
         </is>
       </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3633,6 +3638,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3640,6 +3650,11 @@
           <t>340</t>
         </is>
       </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3647,6 +3662,11 @@
           <t>341</t>
         </is>
       </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3654,6 +3674,11 @@
           <t>342</t>
         </is>
       </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3661,6 +3686,11 @@
           <t>343</t>
         </is>
       </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3668,6 +3698,11 @@
           <t>344</t>
         </is>
       </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -3675,6 +3710,11 @@
           <t>345</t>
         </is>
       </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3682,6 +3722,11 @@
           <t>346</t>
         </is>
       </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3689,6 +3734,11 @@
           <t>347</t>
         </is>
       </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3696,6 +3746,11 @@
           <t>348</t>
         </is>
       </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3703,6 +3758,11 @@
           <t>349</t>
         </is>
       </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3710,6 +3770,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -3717,6 +3782,11 @@
           <t>350</t>
         </is>
       </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 3C, 3D, 3E</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -3724,6 +3794,11 @@
           <t>351</t>
         </is>
       </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -3731,6 +3806,11 @@
           <t>352</t>
         </is>
       </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -3738,6 +3818,11 @@
           <t>353</t>
         </is>
       </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>1, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 1K, 1L, 1M, 1N, 2A, 2B, 3A, 3B1A, 3B1B, 3B2A, 3B2B, 3B3A, 3B3B, 3C1, 3C10A1, 3C10A2, 3C10B, 3C2, 3C3A1, 3C3A2, 3C3B, 3C4A1, 3C4A2, 3C4B, 3C5A, 3C5B, 3C6A, 3C6B, 3C7A, 3C7B, 3C8A, 3C8B, 3C9A, 3C9B, 3D</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -3745,6 +3830,11 @@
           <t>354</t>
         </is>
       </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 19, 2, 20A, 20B, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 6, 60, 61, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -3752,6 +3842,11 @@
           <t>355A</t>
         </is>
       </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2A, 2B1, 2B2, 2C, 2D, 2E, 2F</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -3759,6 +3854,11 @@
           <t>355B</t>
         </is>
       </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2A1, 2A2, 2A3, 2A4A, 2A4B, 2B10, 2B11, 2B12, 2B13, 2B14, 2B15A, 2B15B, 2B16A1, 2B16A2, 2B16B, 2B17, 2B18, 2B19, 2B1A, 2B1B, 2B2, 2B20, 2B21, 2B22, 2B23, 2B24, 2B25, 2B26, 2B27, 2B28, 2B29, 2B3, 2B30, 2B31, 2B32, 2B33, 2B34, 2B35, 2B36A1, 2B36A2, 2B36B, 2B37A, 2B38, 2B39, 2B4, 2B40, 2B41, 2B42, 2B43A1, 2B43B, 2B44, 2B45, 2B46, 2B47A, 2B47B1, 2B47B2, 2B5, 2B61A, 2B61B1, 2B61B2, 2B6A1, 2B6A2A, 2B6A2B, 2B7A1, 2B7A2, 2B7B, 2B7C, 2B8, 2B9, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -3766,6 +3866,11 @@
           <t>356</t>
         </is>
       </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A2, 1A3, 1B1, 1B2, 1C1, 1C2A, 1C2B, 1D1, 1D1A1A, 1D2, 1D3A1A, 1D3B, 1D3C, 1E, 1F, 1G1, 1G2, 1H, 1I1, 1I2, 1J1, 1J2, 1K1A, 1K1B, 1K1C, 1K2, 1L, 1M, 1N1, 1N2, 2, 3, 4, 6A, 6B, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -3773,6 +3878,11 @@
           <t>357</t>
         </is>
       </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -3780,6 +3890,11 @@
           <t>358</t>
         </is>
       </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -3787,6 +3902,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -3794,6 +3914,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -3801,6 +3926,11 @@
           <t>360</t>
         </is>
       </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -3808,6 +3938,11 @@
           <t>361</t>
         </is>
       </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -3815,6 +3950,11 @@
           <t>362</t>
         </is>
       </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -3822,6 +3962,11 @@
           <t>363</t>
         </is>
       </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -3829,6 +3974,11 @@
           <t>364</t>
         </is>
       </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -3836,6 +3986,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 4, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -3843,6 +3998,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -3850,6 +4010,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -3857,6 +4022,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -3864,6 +4034,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -3871,6 +4046,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -3878,6 +4058,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -3885,6 +4070,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -3892,6 +4082,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -3899,6 +4094,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -3906,6 +4106,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A1, 3A2, 3B, 4A, 4B, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -3913,6 +4118,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -3920,6 +4130,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4, 5A, 5B, 6A, 6B, 7A, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -3927,6 +4142,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -3934,6 +4154,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 18C, 19, 2, 20, 21, 22, 23, 24A, 24B, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 5A1A1, 6, 7A1A1, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -3941,6 +4166,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -3948,6 +4178,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -3955,6 +4190,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -3962,6 +4202,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -3969,6 +4214,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -3976,6 +4226,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6A, 6B, 6C, 7, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -3983,6 +4238,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -3990,6 +4250,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -3997,6 +4262,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -4004,6 +4274,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -4011,6 +4286,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -4018,6 +4298,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -4025,6 +4310,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 8</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -4032,6 +4322,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -4039,6 +4334,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -4046,6 +4346,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -4053,6 +4358,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -4060,6 +4370,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -4067,6 +4382,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -4074,6 +4394,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -4081,6 +4406,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -4088,6 +4418,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A1, 3A2, 3A3, 3B, 4A1, 4A2, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -4095,6 +4430,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -4102,6 +4442,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -4109,6 +4454,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -4116,6 +4466,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -4123,6 +4478,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -4130,6 +4490,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -4137,6 +4502,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -4144,6 +4514,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -4151,6 +4526,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -4158,6 +4538,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -4165,6 +4550,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -4172,6 +4562,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -4179,6 +4574,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -4186,6 +4586,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -4193,6 +4598,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 2I, 2J, 3A, 3B, 3C, 3D1, 3D2, 3E, 3F1, 3F2, 3G, 3H1, 3H2, 3I1, 3I2, 3J1, 3J2, 3K, 3L, 3M, 3N, 3O, 3P1, 3P2, 4A1, 4A2, 4B, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -4200,6 +4610,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -4207,6 +4622,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -4214,6 +4634,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -4221,6 +4646,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -4228,6 +4658,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -4235,6 +4670,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -4242,6 +4682,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -4249,6 +4694,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -4256,6 +4706,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -4263,6 +4718,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -4270,6 +4730,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -4277,11 +4742,21 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 2, 3A, 3B, 4, 5, 6, 7A, 7B, 8A1, 8A2, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
           <t>95</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>1, 2</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
@@ -4766,6 +4766,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -4773,6 +4778,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -4780,11 +4790,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 1A, 1B, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>1, 2</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
@@ -662,6 +662,11 @@
           <t>116</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -669,6 +674,11 @@
           <t>117</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -676,6 +686,11 @@
           <t>118</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -683,6 +698,11 @@
           <t>119</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 5C, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -690,6 +710,11 @@
           <t>12</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -697,6 +722,11 @@
           <t>120</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 4D, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -704,6 +734,11 @@
           <t>121</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -711,6 +746,11 @@
           <t>122</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -718,6 +758,11 @@
           <t>123</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 6, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 7, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 8, 80A, 80B, 80C, 80D, 81, 9</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -725,6 +770,11 @@
           <t>124</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -732,6 +782,11 @@
           <t>125</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -739,6 +794,11 @@
           <t>126</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1A1A1A, 1A1A2, 1A1B, 1A2, 1B, 1C, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -746,6 +806,11 @@
           <t>127</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1J</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -753,6 +818,11 @@
           <t>128</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>10, 11, 1A1A1A1A, 1A1A2, 1A1B, 1A1C, 1A1D, 1A2, 1B, 3A1, 3A2, 3A3, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -760,6 +830,11 @@
           <t>129</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -767,6 +842,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2, 2B, 3, 4, 5, 6, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -774,6 +854,11 @@
           <t>130</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -781,6 +866,11 @@
           <t>131</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -788,6 +878,11 @@
           <t>132</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -795,6 +890,11 @@
           <t>133</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B1, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -802,6 +902,11 @@
           <t>134</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1A, 1B1A, 1B1B, 1B2, 1C1A, 1C1B, 1C2, 2A1A, 2A1B, 2A2, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -809,6 +914,11 @@
           <t>135</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -816,6 +926,11 @@
           <t>136</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -823,6 +938,11 @@
           <t>137</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -830,6 +950,11 @@
           <t>138</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -837,6 +962,11 @@
           <t>139</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -844,6 +974,11 @@
           <t>14</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 3B, 3C1, 3C2</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -851,6 +986,11 @@
           <t>140</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -858,6 +998,11 @@
           <t>141</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -865,6 +1010,11 @@
           <t>142</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -872,6 +1022,11 @@
           <t>143</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -879,6 +1034,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -886,6 +1046,11 @@
           <t>145</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -893,6 +1058,11 @@
           <t>146</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -900,6 +1070,11 @@
           <t>147</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -907,6 +1082,11 @@
           <t>148</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -914,6 +1094,11 @@
           <t>149</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -921,6 +1106,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -928,6 +1118,11 @@
           <t>150</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 5A1, 5B1A1A1, 6A1, 7, 8A, 8B1A1, 8B1A1B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -935,6 +1130,11 @@
           <t>151</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -942,6 +1142,11 @@
           <t>152</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -949,6 +1154,11 @@
           <t>153</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -956,6 +1166,11 @@
           <t>154</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -963,6 +1178,11 @@
           <t>155</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -970,6 +1190,11 @@
           <t>156</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -977,6 +1202,11 @@
           <t>157</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4A, 4B, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -984,6 +1214,11 @@
           <t>158</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -991,6 +1226,11 @@
           <t>159</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -998,6 +1238,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1005,6 +1250,11 @@
           <t>160</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 2, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1012,6 +1262,11 @@
           <t>161</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1019,6 +1274,11 @@
           <t>162</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1026,6 +1286,11 @@
           <t>163</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1033,6 +1298,11 @@
           <t>164</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A, 4B1, 4B2</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1040,6 +1310,11 @@
           <t>165</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1047,6 +1322,11 @@
           <t>166</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 4A, 4B, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1054,6 +1334,11 @@
           <t>167</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1061,6 +1346,11 @@
           <t>168</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1068,6 +1358,11 @@
           <t>169</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1075,6 +1370,11 @@
           <t>17</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1082,6 +1382,11 @@
           <t>170</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1089,6 +1394,11 @@
           <t>171</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1096,6 +1406,11 @@
           <t>172</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1103,6 +1418,11 @@
           <t>173</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1110,6 +1430,11 @@
           <t>174</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1117,6 +1442,11 @@
           <t>175</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1124,6 +1454,11 @@
           <t>176</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1131,6 +1466,11 @@
           <t>177</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1138,6 +1478,11 @@
           <t>178</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1145,6 +1490,11 @@
           <t>179</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1152,6 +1502,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 2C, 2D, 3</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1159,6 +1514,11 @@
           <t>180</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1166,6 +1526,11 @@
           <t>181</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1173,6 +1538,11 @@
           <t>182</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1180,6 +1550,11 @@
           <t>183</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1187,6 +1562,11 @@
           <t>184</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1194,6 +1574,11 @@
           <t>185</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1201,6 +1586,11 @@
           <t>186</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1208,6 +1598,11 @@
           <t>187</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1215,6 +1610,11 @@
           <t>188</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 5C, 5D, 5E</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1222,6 +1622,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3, 2B, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1229,6 +1634,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1236,6 +1646,11 @@
           <t>190</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1243,6 +1658,11 @@
           <t>191</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1250,6 +1670,11 @@
           <t>192</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A1, 2A2, 2B, 3A, 3B, 3C1, 3C2, 4</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1257,6 +1682,11 @@
           <t>193</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 2A, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1264,6 +1694,11 @@
           <t>194</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1271,6 +1706,11 @@
           <t>195</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1278,6 +1718,11 @@
           <t>196</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1285,6 +1730,11 @@
           <t>197</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1292,6 +1742,11 @@
           <t>198</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1299,11 +1754,21 @@
           <t>199</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A1, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 35, 36, 37, 38, 39, 4, 40, 5, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
@@ -1778,6 +1778,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1785,6 +1790,11 @@
           <t>200</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1792,6 +1802,11 @@
           <t>201</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1799,6 +1814,11 @@
           <t>202</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1806,6 +1826,11 @@
           <t>203</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1813,6 +1838,11 @@
           <t>204</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 3A, 3C, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1820,6 +1850,11 @@
           <t>205</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1827,6 +1862,11 @@
           <t>206</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1834,6 +1874,11 @@
           <t>207</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1841,6 +1886,11 @@
           <t>208</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1848,6 +1898,11 @@
           <t>209</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1855,6 +1910,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1862,6 +1922,11 @@
           <t>210</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1869,6 +1934,11 @@
           <t>211</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1876,6 +1946,11 @@
           <t>212</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1883,6 +1958,11 @@
           <t>213</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1890,6 +1970,11 @@
           <t>214</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 4C, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1897,6 +1982,11 @@
           <t>215</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1904,6 +1994,11 @@
           <t>216</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1911,6 +2006,11 @@
           <t>217</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A1, 3A2, 3A3, 3B, 3C1, 3C2, 3D, 3E, 4</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1918,6 +2018,11 @@
           <t>218</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A1C, 1A1D, 1A2, 1A3, 1A4, 1B, 2, 3, 4, 5A, 5B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1925,6 +2030,11 @@
           <t>219</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1932,6 +2042,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -1939,6 +2054,11 @@
           <t>220</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -1946,6 +2066,11 @@
           <t>221</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -1953,6 +2078,11 @@
           <t>222</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -1960,6 +2090,11 @@
           <t>223</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -1967,6 +2102,11 @@
           <t>224</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -1974,6 +2114,11 @@
           <t>225</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -1981,6 +2126,11 @@
           <t>226</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -1988,6 +2138,11 @@
           <t>227</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -1995,6 +2150,11 @@
           <t>228</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2002,6 +2162,11 @@
           <t>229</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1, 10, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2009,6 +2174,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2016,6 +2186,11 @@
           <t>230</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 3, 4A, 4B, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2023,6 +2198,11 @@
           <t>231</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2030,6 +2210,11 @@
           <t>232</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2037,6 +2222,11 @@
           <t>233</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B, 4A, 4B, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2044,6 +2234,11 @@
           <t>234</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2051,6 +2246,11 @@
           <t>235</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2058,6 +2258,11 @@
           <t>236</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 4, 5A, 5B, 6A, 6B, 6C, 6D, 6E, 6F</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2065,6 +2270,11 @@
           <t>237</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2072,6 +2282,11 @@
           <t>238</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2079,6 +2294,11 @@
           <t>239</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2086,6 +2306,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2093,6 +2318,11 @@
           <t>240</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2100,6 +2330,11 @@
           <t>241</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2107,6 +2342,11 @@
           <t>242</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1, 10, 2A, 2B, 2C, 2D, 2E, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2114,6 +2354,11 @@
           <t>243</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3, 4A, 4B, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2121,6 +2366,11 @@
           <t>244</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3A, 3B, 3C, 3D, 3E, 4, 5, 6A, 6B, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2128,6 +2378,11 @@
           <t>245</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2135,6 +2390,11 @@
           <t>246</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2142,6 +2402,11 @@
           <t>247</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 3A, 3B, 4A, 4B, 4C, 4D, 4E, 4F, 4G</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2149,6 +2414,11 @@
           <t>248</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 2F</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2156,6 +2426,11 @@
           <t>249</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 5A, 5B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2163,6 +2438,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2170,6 +2450,11 @@
           <t>250</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 1K, 1L, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2177,6 +2462,11 @@
           <t>251</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2184,6 +2474,11 @@
           <t>252</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2191,6 +2486,11 @@
           <t>253</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2198,6 +2498,11 @@
           <t>254</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2205,6 +2510,11 @@
           <t>255</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2212,6 +2522,11 @@
           <t>256</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2219,6 +2534,11 @@
           <t>257</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2226,6 +2546,11 @@
           <t>258</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6A, 6B, 6C, 7, 8, 9A, 9B, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2233,6 +2558,11 @@
           <t>259</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2240,6 +2570,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3A, 3B, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2247,6 +2582,11 @@
           <t>260</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6, 7A, 7B, 7C</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2254,6 +2594,11 @@
           <t>261</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2261,6 +2606,11 @@
           <t>262</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2268,6 +2618,11 @@
           <t>263</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2275,6 +2630,11 @@
           <t>264</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2282,6 +2642,11 @@
           <t>265</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2289,6 +2654,11 @@
           <t>266</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2296,6 +2666,11 @@
           <t>267</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2303,6 +2678,11 @@
           <t>268</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2310,6 +2690,11 @@
           <t>269</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2317,6 +2702,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 2, 3A, 3B, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2324,6 +2714,11 @@
           <t>270</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 2D</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2331,6 +2726,11 @@
           <t>271</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2338,6 +2738,11 @@
           <t>272</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2345,6 +2750,11 @@
           <t>273</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2352,6 +2762,11 @@
           <t>274</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>10, 11, 1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2359,6 +2774,11 @@
           <t>275</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2366,6 +2786,11 @@
           <t>276</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 2C, 2D, 2E</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2373,6 +2798,11 @@
           <t>277</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2380,6 +2810,11 @@
           <t>278</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2387,6 +2822,11 @@
           <t>279</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2394,6 +2834,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2401,6 +2846,11 @@
           <t>280</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2408,6 +2858,11 @@
           <t>281</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2415,6 +2870,11 @@
           <t>282</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2422,6 +2882,11 @@
           <t>283</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2429,11 +2894,21 @@
           <t>284</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
           <t>285</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
@@ -2918,6 +2918,11 @@
           <t>286</t>
         </is>
       </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2925,6 +2930,11 @@
           <t>287</t>
         </is>
       </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2932,6 +2942,11 @@
           <t>288</t>
         </is>
       </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2939,6 +2954,11 @@
           <t>289</t>
         </is>
       </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2946,6 +2966,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 2D, 3, 4A1, 4A10, 4A2, 4A3, 4A4, 4A5A, 4A5B, 4A5C, 4A6, 4A7, 4A8, 4A9, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2953,6 +2978,11 @@
           <t>290</t>
         </is>
       </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2960,6 +2990,11 @@
           <t>291</t>
         </is>
       </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2967,6 +3002,11 @@
           <t>292</t>
         </is>
       </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 2</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2974,6 +3014,11 @@
           <t>293</t>
         </is>
       </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2981,6 +3026,11 @@
           <t>294</t>
         </is>
       </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2988,6 +3038,11 @@
           <t>295</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -2995,6 +3050,11 @@
           <t>296</t>
         </is>
       </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -3002,6 +3062,11 @@
           <t>297</t>
         </is>
       </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -3009,6 +3074,11 @@
           <t>298</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -3016,6 +3086,11 @@
           <t>299</t>
         </is>
       </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -3023,6 +3098,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3A, 3B, 4, 5A, 5B, 5C, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -3030,6 +3110,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -3037,6 +3122,11 @@
           <t>300</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -3044,6 +3134,11 @@
           <t>301</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -3051,6 +3146,11 @@
           <t>302</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -3058,6 +3158,11 @@
           <t>303</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -3065,6 +3170,11 @@
           <t>304</t>
         </is>
       </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -3072,6 +3182,11 @@
           <t>305</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -3079,6 +3194,11 @@
           <t>306</t>
         </is>
       </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -3086,6 +3206,11 @@
           <t>307</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -3093,6 +3218,11 @@
           <t>308</t>
         </is>
       </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -3100,6 +3230,11 @@
           <t>309</t>
         </is>
       </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -3107,6 +3242,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3, 4, 5A, 5B, 5C, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -3114,6 +3254,11 @@
           <t>310</t>
         </is>
       </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -3121,6 +3266,11 @@
           <t>311</t>
         </is>
       </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -3128,6 +3278,11 @@
           <t>312</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -3135,6 +3290,11 @@
           <t>313</t>
         </is>
       </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -3142,6 +3302,11 @@
           <t>314</t>
         </is>
       </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -3149,6 +3314,11 @@
           <t>315</t>
         </is>
       </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 1D, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -3156,6 +3326,11 @@
           <t>316</t>
         </is>
       </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1, 1B, 2A, 2B, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -3163,6 +3338,11 @@
           <t>317</t>
         </is>
       </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -3170,6 +3350,11 @@
           <t>318</t>
         </is>
       </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -3177,6 +3362,11 @@
           <t>319</t>
         </is>
       </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -3184,6 +3374,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -3191,6 +3386,11 @@
           <t>320</t>
         </is>
       </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -3198,6 +3398,11 @@
           <t>321</t>
         </is>
       </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -3205,6 +3410,11 @@
           <t>322</t>
         </is>
       </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -3212,6 +3422,11 @@
           <t>323</t>
         </is>
       </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -3219,6 +3434,11 @@
           <t>324</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -3226,6 +3446,11 @@
           <t>325</t>
         </is>
       </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -3233,6 +3458,11 @@
           <t>326</t>
         </is>
       </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -3240,6 +3470,11 @@
           <t>327</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3247,6 +3482,11 @@
           <t>328</t>
         </is>
       </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3254,6 +3494,11 @@
           <t>329</t>
         </is>
       </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3261,6 +3506,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 7C</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3268,6 +3518,11 @@
           <t>330</t>
         </is>
       </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2, 3, 5</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3275,6 +3530,11 @@
           <t>331</t>
         </is>
       </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E1, 2E2, 3A, 3B, 4A, 4B, 5, 6A, 6B, 6C1, 6C2, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3282,6 +3542,11 @@
           <t>332</t>
         </is>
       </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3289,6 +3554,11 @@
           <t>333</t>
         </is>
       </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3296,6 +3566,11 @@
           <t>334</t>
         </is>
       </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3303,6 +3578,11 @@
           <t>335</t>
         </is>
       </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3310,6 +3590,11 @@
           <t>336</t>
         </is>
       </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>1A1A1, 1A1A2, 1A1B, 1A2, 1A3, 1A4, 1B1A, 1B1B, 1B1C, 1B2, 2A1A, 2A1B, 2A1C, 2A1D, 2A2, 2A3, 2B1, 2B2, 2C1, 2C2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3317,6 +3602,11 @@
           <t>337</t>
         </is>
       </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3324,6 +3614,11 @@
           <t>338</t>
         </is>
       </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3331,6 +3626,11 @@
           <t>339</t>
         </is>
       </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3338,6 +3638,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3345,6 +3650,11 @@
           <t>340</t>
         </is>
       </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3352,6 +3662,11 @@
           <t>341</t>
         </is>
       </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3359,6 +3674,11 @@
           <t>342</t>
         </is>
       </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3366,6 +3686,11 @@
           <t>343</t>
         </is>
       </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3373,6 +3698,11 @@
           <t>344</t>
         </is>
       </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -3380,6 +3710,11 @@
           <t>345</t>
         </is>
       </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3387,6 +3722,11 @@
           <t>346</t>
         </is>
       </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3394,6 +3734,11 @@
           <t>347</t>
         </is>
       </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3401,6 +3746,11 @@
           <t>348</t>
         </is>
       </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3408,6 +3758,11 @@
           <t>349</t>
         </is>
       </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3415,6 +3770,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -3422,6 +3782,11 @@
           <t>350</t>
         </is>
       </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 3C, 3D, 3E</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -3429,6 +3794,11 @@
           <t>351</t>
         </is>
       </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -3436,6 +3806,11 @@
           <t>352</t>
         </is>
       </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -3443,6 +3818,11 @@
           <t>353</t>
         </is>
       </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>1, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 1K, 1L, 1M, 1N, 2A, 2B, 3A, 3B1A, 3B1B, 3B2A, 3B2B, 3B3A, 3B3B, 3C1, 3C10A1, 3C10A2, 3C10B, 3C2, 3C3A1, 3C3A2, 3C3B, 3C4A1, 3C4A2, 3C4B, 3C5A, 3C5B, 3C6A, 3C6B, 3C7A, 3C7B, 3C8A, 3C8B, 3C9A, 3C9B, 3D</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -3450,6 +3830,11 @@
           <t>354</t>
         </is>
       </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 17, 18, 19, 2, 20A, 20B, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 6, 60, 61, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -3457,6 +3842,11 @@
           <t>355A</t>
         </is>
       </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2A, 2B1, 2B2, 2C, 2D, 2E, 2F</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -3464,6 +3854,11 @@
           <t>355B</t>
         </is>
       </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2A1, 2A2, 2A3, 2A4A, 2A4B, 2B10, 2B11, 2B12, 2B13, 2B14, 2B15A, 2B15B, 2B16A1, 2B16A2, 2B16B, 2B17, 2B18, 2B19, 2B1A, 2B1B, 2B2, 2B20, 2B21, 2B22, 2B23, 2B24, 2B25, 2B26, 2B27, 2B28, 2B29, 2B3, 2B30, 2B31, 2B32, 2B33, 2B34, 2B35, 2B36A1, 2B36A2, 2B36B, 2B37A, 2B38, 2B39, 2B4, 2B40, 2B41, 2B42, 2B43A1, 2B43B, 2B44, 2B45, 2B46, 2B47A, 2B47B1, 2B47B2, 2B5, 2B61A, 2B61B1, 2B61B2, 2B6A1, 2B6A2A, 2B6A2B, 2B7A1, 2B7A2, 2B7B, 2B7C, 2B8, 2B9, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -3471,6 +3866,11 @@
           <t>356</t>
         </is>
       </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A2, 1A3, 1B1, 1B2, 1C1, 1C2A, 1C2B, 1D1, 1D1A1A, 1D2, 1D3A1A, 1D3B, 1D3C, 1E, 1F, 1G1, 1G2, 1H, 1I1, 1I2, 1J1, 1J2, 1K1A, 1K1B, 1K1C, 1K2, 1L, 1M, 1N1, 1N2, 2, 3, 4, 6A, 6B, 7, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -3478,6 +3878,11 @@
           <t>357</t>
         </is>
       </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -3485,6 +3890,11 @@
           <t>358</t>
         </is>
       </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -3492,6 +3902,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -3499,6 +3914,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -3506,6 +3926,11 @@
           <t>360</t>
         </is>
       </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -3513,6 +3938,11 @@
           <t>361</t>
         </is>
       </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -3520,6 +3950,11 @@
           <t>362</t>
         </is>
       </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -3527,6 +3962,11 @@
           <t>363</t>
         </is>
       </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -3534,6 +3974,11 @@
           <t>364</t>
         </is>
       </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -3541,6 +3986,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 4, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -3548,6 +3998,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -3555,11 +4010,21 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16A, 16B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
           <t>4</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Palavakkam_13.347871_80.072713.xlsx
@@ -4034,6 +4034,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -4041,6 +4046,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -4048,6 +4058,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -4055,6 +4070,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -4062,6 +4082,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -4069,6 +4094,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -4076,6 +4106,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A1, 3A2, 3B, 4A, 4B, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -4083,6 +4118,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -4090,6 +4130,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4, 5A, 5B, 6A, 6B, 7A, 7B, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -4097,6 +4142,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -4104,6 +4154,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18A, 18B, 18C, 19, 2, 20, 21, 22, 23, 24A, 24B, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 50, 51, 52, 5A1A1, 6, 7A1A1, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -4111,6 +4166,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -4118,6 +4178,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -4125,6 +4190,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -4132,6 +4202,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -4139,6 +4214,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -4146,6 +4226,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6A, 6B, 6C, 7, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -4153,6 +4238,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -4160,6 +4250,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -4167,6 +4262,11 @@
           <t>58</t>
         </is>
       </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -4174,6 +4274,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -4181,6 +4286,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -4188,6 +4298,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -4195,6 +4310,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 8</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -4202,6 +4322,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -4209,6 +4334,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -4216,6 +4346,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -4223,6 +4358,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -4230,6 +4370,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -4237,6 +4382,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -4244,6 +4394,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -4251,6 +4406,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -4258,6 +4418,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A1, 3A2, 3A3, 3B, 4A1, 4A2, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -4265,6 +4430,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -4272,6 +4442,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -4279,6 +4454,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -4286,6 +4466,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -4293,6 +4478,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -4300,6 +4490,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -4307,6 +4502,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -4314,6 +4514,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -4321,6 +4526,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -4328,6 +4538,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -4335,6 +4550,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13A, 13B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -4342,6 +4562,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -4349,6 +4574,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -4356,6 +4586,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -4363,6 +4598,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H, 2I, 2J, 3A, 3B, 3C, 3D1, 3D2, 3E, 3F1, 3F2, 3G, 3H1, 3H2, 3I1, 3I2, 3J1, 3J2, 3K, 3L, 3M, 3N, 3O, 3P1, 3P2, 4A1, 4A2, 4B, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -4370,6 +4610,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -4377,6 +4622,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -4384,6 +4634,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -4391,6 +4646,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -4398,6 +4658,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -4405,6 +4670,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -4412,6 +4682,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -4419,6 +4694,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -4426,6 +4706,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -4433,6 +4718,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -4440,6 +4730,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -4447,6 +4742,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 2, 3A, 3B, 4, 5, 6, 7A, 7B, 8A1, 8A2, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -4454,6 +4754,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -4461,6 +4766,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -4468,6 +4778,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -4475,11 +4790,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 1A, 1B, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>1, 2</t>
         </is>
       </c>
     </row>
